--- a/myCBD/myInfo/Race Code and Names.xlsx
+++ b/myCBD/myInfo/Race Code and Names.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\0.CBD\myCBD\myInfo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="480" yWindow="105" windowWidth="27795" windowHeight="12600"/>
   </bookViews>
@@ -16,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>-missing</t>
   </si>
@@ -85,12 +90,54 @@
   </si>
   <si>
     <t>Native American/Alaska Native</t>
+  </si>
+  <si>
+    <t>raceCode</t>
+  </si>
+  <si>
+    <t>raceCode2</t>
+  </si>
+  <si>
+    <t>raceCode3</t>
+  </si>
+  <si>
+    <t>raceCode4</t>
+  </si>
+  <si>
+    <t>raceCode5</t>
+  </si>
+  <si>
+    <t>White*</t>
+  </si>
+  <si>
+    <t>Black*</t>
+  </si>
+  <si>
+    <t>Native American*</t>
+  </si>
+  <si>
+    <t>Asian*</t>
+  </si>
+  <si>
+    <t>Hawaiian/PI*</t>
+  </si>
+  <si>
+    <t>Other*</t>
+  </si>
+  <si>
+    <t>Multirace*</t>
+  </si>
+  <si>
+    <t>unknown*</t>
+  </si>
+  <si>
+    <t>Latino/Hispanic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -132,6 +179,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -180,7 +230,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -215,7 +265,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -424,133 +474,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:D12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="22.7109375" customWidth="1"/>
     <col min="4" max="4" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="D11" t="s">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
+      <c r="E11" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
